--- a/data-cleaning/verified/导入_2022年1号机A修.xlsx
+++ b/data-cleaning/verified/导入_2022年1号机A修.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F001-W001</t>
+          <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W002</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W003</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F004-W004</t>
+          <t>1G-GGRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F005-W005</t>
+          <t>1G-GGRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F006-W006</t>
+          <t>1G-GGRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F007-W007</t>
+          <t>1G-GGRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F008-W008</t>
+          <t>1G-GGRQ-GQ-L001-F008-W</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F009-W009</t>
+          <t>1G-GGRQ-GQ-L001-F009-W</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F010-W010</t>
+          <t>1G-GGRQ-GQ-L001-F010-W</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F011-W011</t>
+          <t>1G-GGRQ-GQ-L001-F011-W</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F012-W012</t>
+          <t>1G-GGRQ-GQ-L001-F012-W</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F001-W013</t>
+          <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W014</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W015</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F004-W016</t>
+          <t>1G-GGRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F005-W017</t>
+          <t>1G-GGRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F006-W018</t>
+          <t>1G-GGRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F007-W019</t>
+          <t>1G-GGRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F008-W020</t>
+          <t>1G-GGRQ-GQ-L003-F008-W</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F009-W021</t>
+          <t>1G-GGRQ-GQ-L003-F009-W</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F010-W022</t>
+          <t>1G-GGRQ-GQ-L003-F010-W</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F011-W023</t>
+          <t>1G-GGRQ-GQ-L003-F011-W</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F012-W024</t>
+          <t>1G-GGRQ-GQ-L003-F012-W</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F001-W025</t>
+          <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W026</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W027</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F004-W028</t>
+          <t>1G-GGRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F005-W029</t>
+          <t>1G-GGRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F006-W030</t>
+          <t>1G-GGRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F007-W031</t>
+          <t>1G-GGRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F008-W032</t>
+          <t>1G-GGRQ-GQ-L005-F008-W</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F009-W033</t>
+          <t>1G-GGRQ-GQ-L005-F009-W</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F010-W034</t>
+          <t>1G-GGRQ-GQ-L005-F010-W</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F011-W035</t>
+          <t>1G-GGRQ-GQ-L005-F011-W</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F012-W036</t>
+          <t>1G-GGRQ-GQ-L005-F012-W</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F001-W037</t>
+          <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W038</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W039</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F004-W040</t>
+          <t>1G-GGRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F005-W041</t>
+          <t>1G-GGRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F006-W042</t>
+          <t>1G-GGRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F007-W043</t>
+          <t>1G-GGRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F008-W044</t>
+          <t>1G-GGRQ-GQ-L007-F008-W</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F009-W045</t>
+          <t>1G-GGRQ-GQ-L007-F009-W</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F010-W046</t>
+          <t>1G-GGRQ-GQ-L007-F010-W</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F011-W047</t>
+          <t>1G-GGRQ-GQ-L007-F011-W</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F012-W048</t>
+          <t>1G-GGRQ-GQ-L007-F012-W</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F001-W049</t>
+          <t>1G-GGRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F002-W050</t>
+          <t>1G-GGRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F003-W051</t>
+          <t>1G-GGRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F004-W052</t>
+          <t>1G-GGRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F005-W053</t>
+          <t>1G-GGRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F006-W054</t>
+          <t>1G-GGRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F007-W055</t>
+          <t>1G-GGRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F008-W056</t>
+          <t>1G-GGRQ-GQ-R001-F008-W</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F009-W057</t>
+          <t>1G-GGRQ-GQ-R001-F009-W</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F010-W058</t>
+          <t>1G-GGRQ-GQ-R001-F010-W</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F011-W059</t>
+          <t>1G-GGRQ-GQ-R001-F011-W</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F012-W060</t>
+          <t>1G-GGRQ-GQ-R001-F012-W</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F001-W061</t>
+          <t>1G-GGRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F002-W062</t>
+          <t>1G-GGRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F003-W063</t>
+          <t>1G-GGRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F004-W064</t>
+          <t>1G-GGRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F005-W065</t>
+          <t>1G-GGRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F006-W066</t>
+          <t>1G-GGRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F007-W067</t>
+          <t>1G-GGRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F008-W068</t>
+          <t>1G-GGRQ-GQ-R003-F008-W</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F009-W069</t>
+          <t>1G-GGRQ-GQ-R003-F009-W</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F010-W070</t>
+          <t>1G-GGRQ-GQ-R003-F010-W</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F011-W071</t>
+          <t>1G-GGRQ-GQ-R003-F011-W</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F012-W072</t>
+          <t>1G-GGRQ-GQ-R003-F012-W</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F001-W073</t>
+          <t>1G-GGRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F002-W074</t>
+          <t>1G-GGRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F003-W075</t>
+          <t>1G-GGRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F004-W076</t>
+          <t>1G-GGRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F005-W077</t>
+          <t>1G-GGRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F006-W078</t>
+          <t>1G-GGRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F007-W079</t>
+          <t>1G-GGRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F008-W080</t>
+          <t>1G-GGRQ-GQ-R005-F008-W</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F009-W081</t>
+          <t>1G-GGRQ-GQ-R005-F009-W</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F010-W082</t>
+          <t>1G-GGRQ-GQ-R005-F010-W</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F011-W083</t>
+          <t>1G-GGRQ-GQ-R005-F011-W</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F012-W084</t>
+          <t>1G-GGRQ-GQ-R005-F012-W</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr"/>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F001-W085</t>
+          <t>1G-GGRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F002-W086</t>
+          <t>1G-GGRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F003-W087</t>
+          <t>1G-GGRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F004-W088</t>
+          <t>1G-GGRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F005-W089</t>
+          <t>1G-GGRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F006-W090</t>
+          <t>1G-GGRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr"/>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F007-W091</t>
+          <t>1G-GGRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F008-W092</t>
+          <t>1G-GGRQ-GQ-R007-F008-W</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr"/>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F009-W093</t>
+          <t>1G-GGRQ-GQ-R007-F009-W</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F010-W094</t>
+          <t>1G-GGRQ-GQ-R007-F010-W</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F011-W095</t>
+          <t>1G-GGRQ-GQ-R007-F011-W</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F012-W096</t>
+          <t>1G-GGRQ-GQ-R007-F012-W</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F001-W097</t>
+          <t>1G-GZRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F002-W098</t>
+          <t>1G-GZRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F003-W099</t>
+          <t>1G-GZRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F004-W100</t>
+          <t>1G-GZRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F005-W101</t>
+          <t>1G-GZRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F006-W102</t>
+          <t>1G-GZRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F007-W103</t>
+          <t>1G-GZRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F001-W104</t>
+          <t>1G-GZRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F002-W105</t>
+          <t>1G-GZRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F003-W106</t>
+          <t>1G-GZRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F004-W107</t>
+          <t>1G-GZRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F005-W108</t>
+          <t>1G-GZRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F006-W109</t>
+          <t>1G-GZRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F007-W110</t>
+          <t>1G-GZRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F001-W111</t>
+          <t>1G-GZRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F002-W112</t>
+          <t>1G-GZRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F003-W113</t>
+          <t>1G-GZRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F004-W114</t>
+          <t>1G-GZRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F005-W115</t>
+          <t>1G-GZRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F006-W116</t>
+          <t>1G-GZRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F007-W117</t>
+          <t>1G-GZRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F001-W118</t>
+          <t>1G-GZRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F002-W119</t>
+          <t>1G-GZRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F003-W120</t>
+          <t>1G-GZRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F004-W121</t>
+          <t>1G-GZRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F005-W122</t>
+          <t>1G-GZRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F006-W123</t>
+          <t>1G-GZRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F007-W124</t>
+          <t>1G-GZRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F001-W125</t>
+          <t>1G-GZRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F002-W126</t>
+          <t>1G-GZRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F003-W127</t>
+          <t>1G-GZRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F004-W128</t>
+          <t>1G-GZRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F005-W129</t>
+          <t>1G-GZRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F006-W130</t>
+          <t>1G-GZRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F007-W131</t>
+          <t>1G-GZRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F001-W132</t>
+          <t>1G-GZRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F002-W133</t>
+          <t>1G-GZRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F003-W134</t>
+          <t>1G-GZRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F004-W135</t>
+          <t>1G-GZRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F005-W136</t>
+          <t>1G-GZRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F006-W137</t>
+          <t>1G-GZRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F007-W138</t>
+          <t>1G-GZRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F001-W139</t>
+          <t>1G-GZRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F002-W140</t>
+          <t>1G-GZRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F003-W141</t>
+          <t>1G-GZRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F004-W142</t>
+          <t>1G-GZRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F005-W143</t>
+          <t>1G-GZRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F006-W144</t>
+          <t>1G-GZRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F007-W145</t>
+          <t>1G-GZRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F001-W146</t>
+          <t>1G-GZRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F002-W147</t>
+          <t>1G-GZRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F003-W148</t>
+          <t>1G-GZRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F004-W149</t>
+          <t>1G-GZRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F005-W150</t>
+          <t>1G-GZRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F006-W151</t>
+          <t>1G-GZRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F007-W152</t>
+          <t>1G-GZRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">

--- a/data-cleaning/verified/导入_2022年1号机A修.xlsx
+++ b/data-cleaning/verified/导入_2022年1号机A修.xlsx
@@ -631,7 +631,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -967,7 +967,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1135,7 +1135,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1471,7 +1471,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1639,7 +1639,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1807,7 +1807,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1975,7 +1975,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2311,7 +2311,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2479,7 +2479,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2647,7 +2647,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2815,7 +2815,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2983,7 +2983,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3151,7 +3151,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3319,7 +3319,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3487,7 +3487,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3655,7 +3655,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3823,7 +3823,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3991,7 +3991,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4159,7 +4159,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4327,7 +4327,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4495,7 +4495,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4663,7 +4663,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4831,7 +4831,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4999,7 +4999,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5167,7 +5167,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5335,7 +5335,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5503,7 +5503,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -5671,7 +5671,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5755,7 +5755,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -5839,7 +5839,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6007,7 +6007,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6175,7 +6175,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6259,7 +6259,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6343,7 +6343,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6679,7 +6679,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -6847,7 +6847,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7015,7 +7015,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7183,7 +7183,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7351,7 +7351,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7519,7 +7519,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7603,7 +7603,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -7687,7 +7687,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8023,7 +8023,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8191,7 +8191,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8275,7 +8275,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8359,7 +8359,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -8527,7 +8527,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -8699,7 +8699,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -8875,7 +8875,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9051,7 +9051,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9139,7 +9139,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9227,7 +9227,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9315,7 +9315,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -9403,7 +9403,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -9579,7 +9579,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -9755,7 +9755,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -9931,7 +9931,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10107,7 +10107,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10283,7 +10283,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -10459,7 +10459,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -10547,7 +10547,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -10635,7 +10635,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -10723,7 +10723,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -10811,7 +10811,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -10987,7 +10987,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11163,7 +11163,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11339,7 +11339,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -11427,7 +11427,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -11515,7 +11515,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -11691,7 +11691,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -11867,7 +11867,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12043,7 +12043,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -12219,7 +12219,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -12395,7 +12395,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -12571,7 +12571,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -12659,7 +12659,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -12747,7 +12747,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -12923,7 +12923,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -13099,7 +13099,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -13187,7 +13187,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -13363,7 +13363,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -13451,7 +13451,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -13539,7 +13539,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">

--- a/data-cleaning/verified/导入_2022年1号机A修.xlsx
+++ b/data-cleaning/verified/导入_2022年1号机A修.xlsx
@@ -469,7 +469,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="145" customHeight="1">
+    <row r="2" ht="107" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -619,8 +619,16 @@
           <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -631,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -684,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="145" customHeight="1">
+    <row r="3" ht="107" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -703,8 +711,16 @@
           <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
@@ -715,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -768,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="145" customHeight="1">
+    <row r="4" ht="107" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -787,8 +803,16 @@
           <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -799,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -852,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="145" customHeight="1">
+    <row r="5" ht="107" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -871,8 +895,16 @@
           <t>1G-GGRQ-GQ-L001-F004-W</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
@@ -883,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -936,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="145" customHeight="1">
+    <row r="6" ht="107" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -955,8 +987,16 @@
           <t>1G-GGRQ-GQ-L001-F005-W</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
@@ -967,7 +1007,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1020,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="145" customHeight="1">
+    <row r="7" ht="107" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1039,8 +1079,16 @@
           <t>1G-GGRQ-GQ-L001-F006-W</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
@@ -1051,7 +1099,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1104,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="145" customHeight="1">
+    <row r="8" ht="107" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1123,8 +1171,16 @@
           <t>1G-GGRQ-GQ-L001-F007-W</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
@@ -1135,7 +1191,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1188,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="145" customHeight="1">
+    <row r="9" ht="107" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1207,8 +1263,16 @@
           <t>1G-GGRQ-GQ-L001-F008-W</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
@@ -1219,7 +1283,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1272,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="145" customHeight="1">
+    <row r="10" ht="107" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1291,8 +1355,16 @@
           <t>1G-GGRQ-GQ-L001-F009-W</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
@@ -1303,7 +1375,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1356,7 +1428,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="145" customHeight="1">
+    <row r="11" ht="107" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1375,8 +1447,16 @@
           <t>1G-GGRQ-GQ-L001-F010-W</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
@@ -1387,7 +1467,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1440,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="145" customHeight="1">
+    <row r="12" ht="107" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1459,8 +1539,16 @@
           <t>1G-GGRQ-GQ-L001-F011-W</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
@@ -1471,7 +1559,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1524,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="145" customHeight="1">
+    <row r="13" ht="107" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1543,8 +1631,16 @@
           <t>1G-GGRQ-GQ-L001-F012-W</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
@@ -1555,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1608,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="145" customHeight="1">
+    <row r="14" ht="107" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1627,8 +1723,16 @@
           <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
@@ -1639,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1692,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="145" customHeight="1">
+    <row r="15" ht="107" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1711,8 +1815,16 @@
           <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
@@ -1723,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="145" customHeight="1">
+    <row r="16" ht="107" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1795,8 +1907,16 @@
           <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
@@ -1807,7 +1927,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1860,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="145" customHeight="1">
+    <row r="17" ht="107" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1879,8 +1999,16 @@
           <t>1G-GGRQ-GQ-L003-F004-W</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
@@ -1891,7 +2019,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1944,7 +2072,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="145" customHeight="1">
+    <row r="18" ht="107" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1963,8 +2091,16 @@
           <t>1G-GGRQ-GQ-L003-F005-W</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
@@ -1975,7 +2111,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2028,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="145" customHeight="1">
+    <row r="19" ht="107" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2047,8 +2183,16 @@
           <t>1G-GGRQ-GQ-L003-F006-W</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
@@ -2059,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2256,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="145" customHeight="1">
+    <row r="20" ht="107" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2131,8 +2275,16 @@
           <t>1G-GGRQ-GQ-L003-F007-W</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -2143,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2196,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="145" customHeight="1">
+    <row r="21" ht="107" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2215,8 +2367,16 @@
           <t>1G-GGRQ-GQ-L003-F008-W</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
@@ -2227,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2280,7 +2440,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="145" customHeight="1">
+    <row r="22" ht="107" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2299,8 +2459,16 @@
           <t>1G-GGRQ-GQ-L003-F009-W</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
@@ -2311,7 +2479,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2364,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="145" customHeight="1">
+    <row r="23" ht="107" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2383,8 +2551,16 @@
           <t>1G-GGRQ-GQ-L003-F010-W</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
@@ -2395,7 +2571,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2448,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="145" customHeight="1">
+    <row r="24" ht="107" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2467,8 +2643,16 @@
           <t>1G-GGRQ-GQ-L003-F011-W</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
@@ -2479,7 +2663,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2532,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="145" customHeight="1">
+    <row r="25" ht="107" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2551,8 +2735,16 @@
           <t>1G-GGRQ-GQ-L003-F012-W</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
@@ -2563,7 +2755,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2616,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="145" customHeight="1">
+    <row r="26" ht="107" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2635,8 +2827,16 @@
           <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
@@ -2647,7 +2847,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2700,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="145" customHeight="1">
+    <row r="27" ht="107" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2719,8 +2919,16 @@
           <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
@@ -2731,7 +2939,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2784,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="145" customHeight="1">
+    <row r="28" ht="107" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2803,8 +3011,16 @@
           <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
@@ -2815,7 +3031,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2868,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="145" customHeight="1">
+    <row r="29" ht="107" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2887,8 +3103,16 @@
           <t>1G-GGRQ-GQ-L005-F004-W</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
@@ -2899,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2952,7 +3176,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="145" customHeight="1">
+    <row r="30" ht="107" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2971,8 +3195,16 @@
           <t>1G-GGRQ-GQ-L005-F005-W</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
@@ -2983,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3036,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="145" customHeight="1">
+    <row r="31" ht="107" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3055,8 +3287,16 @@
           <t>1G-GGRQ-GQ-L005-F006-W</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
@@ -3067,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3120,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="145" customHeight="1">
+    <row r="32" ht="107" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3139,8 +3379,16 @@
           <t>1G-GGRQ-GQ-L005-F007-W</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
@@ -3151,7 +3399,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3204,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="145" customHeight="1">
+    <row r="33" ht="107" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3223,8 +3471,16 @@
           <t>1G-GGRQ-GQ-L005-F008-W</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
@@ -3235,7 +3491,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3288,7 +3544,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="145" customHeight="1">
+    <row r="34" ht="107" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3307,8 +3563,16 @@
           <t>1G-GGRQ-GQ-L005-F009-W</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
@@ -3319,7 +3583,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3372,7 +3636,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="145" customHeight="1">
+    <row r="35" ht="107" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3391,8 +3655,16 @@
           <t>1G-GGRQ-GQ-L005-F010-W</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
@@ -3403,7 +3675,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3456,7 +3728,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="145" customHeight="1">
+    <row r="36" ht="107" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3475,8 +3747,16 @@
           <t>1G-GGRQ-GQ-L005-F011-W</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
@@ -3487,7 +3767,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3540,7 +3820,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="145" customHeight="1">
+    <row r="37" ht="107" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3559,8 +3839,16 @@
           <t>1G-GGRQ-GQ-L005-F012-W</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
@@ -3571,7 +3859,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3624,7 +3912,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="145" customHeight="1">
+    <row r="38" ht="107" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3643,8 +3931,16 @@
           <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
@@ -3655,7 +3951,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3708,7 +4004,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="145" customHeight="1">
+    <row r="39" ht="107" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3727,8 +4023,16 @@
           <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
@@ -3739,7 +4043,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3792,7 +4096,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="145" customHeight="1">
+    <row r="40" ht="107" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3811,8 +4115,16 @@
           <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
@@ -3823,7 +4135,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3876,7 +4188,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="145" customHeight="1">
+    <row r="41" ht="107" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3895,8 +4207,16 @@
           <t>1G-GGRQ-GQ-L007-F004-W</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
@@ -3907,7 +4227,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3960,7 +4280,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="145" customHeight="1">
+    <row r="42" ht="107" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3979,8 +4299,16 @@
           <t>1G-GGRQ-GQ-L007-F005-W</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
@@ -3991,7 +4319,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4044,7 +4372,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="145" customHeight="1">
+    <row r="43" ht="107" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4063,8 +4391,16 @@
           <t>1G-GGRQ-GQ-L007-F006-W</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
@@ -4075,7 +4411,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4128,7 +4464,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="145" customHeight="1">
+    <row r="44" ht="107" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4147,8 +4483,16 @@
           <t>1G-GGRQ-GQ-L007-F007-W</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
@@ -4159,7 +4503,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4212,7 +4556,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="145" customHeight="1">
+    <row r="45" ht="107" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4231,8 +4575,16 @@
           <t>1G-GGRQ-GQ-L007-F008-W</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
@@ -4243,7 +4595,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4296,7 +4648,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="145" customHeight="1">
+    <row r="46" ht="107" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4315,8 +4667,16 @@
           <t>1G-GGRQ-GQ-L007-F009-W</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
@@ -4327,7 +4687,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4380,7 +4740,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="145" customHeight="1">
+    <row r="47" ht="107" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4399,8 +4759,16 @@
           <t>1G-GGRQ-GQ-L007-F010-W</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
@@ -4411,7 +4779,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4464,7 +4832,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="145" customHeight="1">
+    <row r="48" ht="107" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4483,8 +4851,16 @@
           <t>1G-GGRQ-GQ-L007-F011-W</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
@@ -4495,7 +4871,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4548,7 +4924,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="145" customHeight="1">
+    <row r="49" ht="107" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4567,8 +4943,16 @@
           <t>1G-GGRQ-GQ-L007-F012-W</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
@@ -4579,7 +4963,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4632,7 +5016,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="145" customHeight="1">
+    <row r="50" ht="107" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4651,8 +5035,16 @@
           <t>1G-GGRQ-GQ-R001-F001-W</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
@@ -4663,7 +5055,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4716,7 +5108,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="145" customHeight="1">
+    <row r="51" ht="107" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4735,8 +5127,16 @@
           <t>1G-GGRQ-GQ-R001-F002-W</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
@@ -4747,7 +5147,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4800,7 +5200,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="145" customHeight="1">
+    <row r="52" ht="107" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4819,8 +5219,16 @@
           <t>1G-GGRQ-GQ-R001-F003-W</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
@@ -4831,7 +5239,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4884,7 +5292,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="145" customHeight="1">
+    <row r="53" ht="107" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4903,8 +5311,16 @@
           <t>1G-GGRQ-GQ-R001-F004-W</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr"/>
       <c r="I53" s="4" t="inlineStr">
@@ -4915,7 +5331,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4968,7 +5384,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="145" customHeight="1">
+    <row r="54" ht="107" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4987,8 +5403,16 @@
           <t>1G-GGRQ-GQ-R001-F005-W</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
@@ -4999,7 +5423,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5052,7 +5476,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="145" customHeight="1">
+    <row r="55" ht="107" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5071,8 +5495,16 @@
           <t>1G-GGRQ-GQ-R001-F006-W</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="4" t="inlineStr">
@@ -5083,7 +5515,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5136,7 +5568,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="145" customHeight="1">
+    <row r="56" ht="107" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5155,8 +5587,16 @@
           <t>1G-GGRQ-GQ-R001-F007-W</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
@@ -5167,7 +5607,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5220,7 +5660,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="145" customHeight="1">
+    <row r="57" ht="107" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5239,8 +5679,16 @@
           <t>1G-GGRQ-GQ-R001-F008-W</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr">
@@ -5251,7 +5699,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5304,7 +5752,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="145" customHeight="1">
+    <row r="58" ht="107" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5323,8 +5771,16 @@
           <t>1G-GGRQ-GQ-R001-F009-W</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
@@ -5335,7 +5791,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5388,7 +5844,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="145" customHeight="1">
+    <row r="59" ht="107" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5407,8 +5863,16 @@
           <t>1G-GGRQ-GQ-R001-F010-W</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr">
@@ -5419,7 +5883,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5472,7 +5936,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="145" customHeight="1">
+    <row r="60" ht="107" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5491,8 +5955,16 @@
           <t>1G-GGRQ-GQ-R001-F011-W</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
@@ -5503,7 +5975,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5556,7 +6028,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="145" customHeight="1">
+    <row r="61" ht="107" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5575,8 +6047,16 @@
           <t>1G-GGRQ-GQ-R001-F012-W</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="4" t="inlineStr">
@@ -5587,7 +6067,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -5640,7 +6120,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="145" customHeight="1">
+    <row r="62" ht="107" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5659,8 +6139,16 @@
           <t>1G-GGRQ-GQ-R003-F001-W</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
@@ -5671,7 +6159,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5724,7 +6212,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="145" customHeight="1">
+    <row r="63" ht="107" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5743,8 +6231,16 @@
           <t>1G-GGRQ-GQ-R003-F002-W</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr">
@@ -5755,7 +6251,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -5808,7 +6304,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="145" customHeight="1">
+    <row r="64" ht="107" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5827,8 +6323,16 @@
           <t>1G-GGRQ-GQ-R003-F003-W</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
@@ -5839,7 +6343,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5892,7 +6396,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="145" customHeight="1">
+    <row r="65" ht="107" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5911,8 +6415,16 @@
           <t>1G-GGRQ-GQ-R003-F004-W</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr"/>
       <c r="I65" s="4" t="inlineStr">
@@ -5923,7 +6435,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -5976,7 +6488,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="145" customHeight="1">
+    <row r="66" ht="107" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5995,8 +6507,16 @@
           <t>1G-GGRQ-GQ-R003-F005-W</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
@@ -6007,7 +6527,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6060,7 +6580,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="145" customHeight="1">
+    <row r="67" ht="107" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6079,8 +6599,16 @@
           <t>1G-GGRQ-GQ-R003-F006-W</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr"/>
       <c r="I67" s="4" t="inlineStr">
@@ -6091,7 +6619,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6144,7 +6672,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="145" customHeight="1">
+    <row r="68" ht="107" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6163,8 +6691,16 @@
           <t>1G-GGRQ-GQ-R003-F007-W</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
@@ -6175,7 +6711,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6228,7 +6764,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="145" customHeight="1">
+    <row r="69" ht="107" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6247,8 +6783,16 @@
           <t>1G-GGRQ-GQ-R003-F008-W</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr"/>
       <c r="I69" s="4" t="inlineStr">
@@ -6259,7 +6803,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6312,7 +6856,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="145" customHeight="1">
+    <row r="70" ht="107" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6331,8 +6875,16 @@
           <t>1G-GGRQ-GQ-R003-F009-W</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
@@ -6343,7 +6895,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6396,7 +6948,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="145" customHeight="1">
+    <row r="71" ht="107" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6415,8 +6967,16 @@
           <t>1G-GGRQ-GQ-R003-F010-W</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr"/>
       <c r="I71" s="4" t="inlineStr">
@@ -6427,7 +6987,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6480,7 +7040,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="145" customHeight="1">
+    <row r="72" ht="107" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6499,8 +7059,16 @@
           <t>1G-GGRQ-GQ-R003-F011-W</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
@@ -6511,7 +7079,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6564,7 +7132,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="145" customHeight="1">
+    <row r="73" ht="107" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6583,8 +7151,16 @@
           <t>1G-GGRQ-GQ-R003-F012-W</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr"/>
       <c r="I73" s="4" t="inlineStr">
@@ -6595,7 +7171,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6648,7 +7224,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="145" customHeight="1">
+    <row r="74" ht="107" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6667,8 +7243,16 @@
           <t>1G-GGRQ-GQ-R005-F001-W</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
@@ -6679,7 +7263,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -6732,7 +7316,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="145" customHeight="1">
+    <row r="75" ht="107" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6751,8 +7335,16 @@
           <t>1G-GGRQ-GQ-R005-F002-W</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr"/>
       <c r="I75" s="4" t="inlineStr">
@@ -6763,7 +7355,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -6816,7 +7408,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="145" customHeight="1">
+    <row r="76" ht="107" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6835,8 +7427,16 @@
           <t>1G-GGRQ-GQ-R005-F003-W</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
@@ -6847,7 +7447,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -6900,7 +7500,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="145" customHeight="1">
+    <row r="77" ht="107" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6919,8 +7519,16 @@
           <t>1G-GGRQ-GQ-R005-F004-W</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr">
@@ -6931,7 +7539,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -6984,7 +7592,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="145" customHeight="1">
+    <row r="78" ht="107" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7003,8 +7611,16 @@
           <t>1G-GGRQ-GQ-R005-F005-W</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
@@ -7015,7 +7631,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7068,7 +7684,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="145" customHeight="1">
+    <row r="79" ht="107" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7087,8 +7703,16 @@
           <t>1G-GGRQ-GQ-R005-F006-W</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr"/>
       <c r="I79" s="4" t="inlineStr">
@@ -7099,7 +7723,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7152,7 +7776,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="145" customHeight="1">
+    <row r="80" ht="107" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7171,8 +7795,16 @@
           <t>1G-GGRQ-GQ-R005-F007-W</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
@@ -7183,7 +7815,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7236,7 +7868,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="145" customHeight="1">
+    <row r="81" ht="107" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7255,8 +7887,16 @@
           <t>1G-GGRQ-GQ-R005-F008-W</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr"/>
       <c r="I81" s="4" t="inlineStr">
@@ -7267,7 +7907,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7320,7 +7960,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="145" customHeight="1">
+    <row r="82" ht="107" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7339,8 +7979,16 @@
           <t>1G-GGRQ-GQ-R005-F009-W</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
@@ -7351,7 +7999,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7404,7 +8052,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="145" customHeight="1">
+    <row r="83" ht="107" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7423,8 +8071,16 @@
           <t>1G-GGRQ-GQ-R005-F010-W</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr">
@@ -7435,7 +8091,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7488,7 +8144,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="145" customHeight="1">
+    <row r="84" ht="107" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7507,8 +8163,16 @@
           <t>1G-GGRQ-GQ-R005-F011-W</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
@@ -7519,7 +8183,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7572,7 +8236,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="145" customHeight="1">
+    <row r="85" ht="107" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7591,8 +8255,16 @@
           <t>1G-GGRQ-GQ-R005-F012-W</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr"/>
       <c r="I85" s="4" t="inlineStr">
@@ -7603,7 +8275,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -7656,7 +8328,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="145" customHeight="1">
+    <row r="86" ht="107" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7675,8 +8347,16 @@
           <t>1G-GGRQ-GQ-R007-F001-W</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
@@ -7687,7 +8367,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -7740,7 +8420,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="145" customHeight="1">
+    <row r="87" ht="107" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7759,8 +8439,16 @@
           <t>1G-GGRQ-GQ-R007-F002-W</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr"/>
       <c r="I87" s="4" t="inlineStr">
@@ -7771,7 +8459,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -7824,7 +8512,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="145" customHeight="1">
+    <row r="88" ht="107" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7843,8 +8531,16 @@
           <t>1G-GGRQ-GQ-R007-F003-W</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
@@ -7855,7 +8551,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -7908,7 +8604,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="145" customHeight="1">
+    <row r="89" ht="107" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7927,8 +8623,16 @@
           <t>1G-GGRQ-GQ-R007-F004-W</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr"/>
       <c r="I89" s="4" t="inlineStr">
@@ -7939,7 +8643,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -7992,7 +8696,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="145" customHeight="1">
+    <row r="90" ht="107" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8011,8 +8715,16 @@
           <t>1G-GGRQ-GQ-R007-F005-W</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
@@ -8023,7 +8735,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8076,7 +8788,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="145" customHeight="1">
+    <row r="91" ht="107" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8095,8 +8807,16 @@
           <t>1G-GGRQ-GQ-R007-F006-W</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr"/>
       <c r="I91" s="4" t="inlineStr">
@@ -8107,7 +8827,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8160,7 +8880,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="145" customHeight="1">
+    <row r="92" ht="107" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8179,8 +8899,16 @@
           <t>1G-GGRQ-GQ-R007-F007-W</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
@@ -8191,7 +8919,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8244,7 +8972,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="145" customHeight="1">
+    <row r="93" ht="107" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8263,8 +8991,16 @@
           <t>1G-GGRQ-GQ-R007-F008-W</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr"/>
       <c r="I93" s="4" t="inlineStr">
@@ -8275,7 +9011,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8328,7 +9064,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="145" customHeight="1">
+    <row r="94" ht="107" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8347,8 +9083,16 @@
           <t>1G-GGRQ-GQ-R007-F009-W</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
@@ -8359,7 +9103,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -8412,7 +9156,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="145" customHeight="1">
+    <row r="95" ht="107" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8431,8 +9175,16 @@
           <t>1G-GGRQ-GQ-R007-F010-W</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr"/>
       <c r="I95" s="4" t="inlineStr">
@@ -8443,7 +9195,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -8496,7 +9248,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="145" customHeight="1">
+    <row r="96" ht="107" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8515,8 +9267,16 @@
           <t>1G-GGRQ-GQ-R007-F011-W</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
@@ -8527,7 +9287,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -8580,7 +9340,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="145" customHeight="1">
+    <row r="97" ht="107" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8599,8 +9359,16 @@
           <t>1G-GGRQ-GQ-R007-F012-W</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr">
@@ -8611,7 +9379,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -8664,7 +9432,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="126" customHeight="1">
+    <row r="98" ht="107" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8688,7 +9456,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
@@ -8699,7 +9471,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -8752,7 +9524,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="126" customHeight="1">
+    <row r="99" ht="107" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8776,7 +9548,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr">
@@ -8787,7 +9563,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -8840,7 +9616,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="126" customHeight="1">
+    <row r="100" ht="107" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8864,7 +9640,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
@@ -8875,7 +9655,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -8928,7 +9708,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="126" customHeight="1">
+    <row r="101" ht="107" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8952,7 +9732,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr"/>
       <c r="I101" s="4" t="inlineStr">
@@ -8963,7 +9747,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9016,7 +9800,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="126" customHeight="1">
+    <row r="102" ht="107" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9040,7 +9824,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
@@ -9051,7 +9839,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9104,7 +9892,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="126" customHeight="1">
+    <row r="103" ht="107" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9128,7 +9916,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr">
@@ -9139,7 +9931,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9192,7 +9984,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="126" customHeight="1">
+    <row r="104" ht="107" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9216,7 +10008,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
@@ -9227,7 +10023,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9280,7 +10076,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="126" customHeight="1">
+    <row r="105" ht="107" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9304,7 +10100,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr">
@@ -9315,7 +10115,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -9368,7 +10168,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="126" customHeight="1">
+    <row r="106" ht="107" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9392,7 +10192,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
@@ -9403,7 +10207,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -9456,7 +10260,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="126" customHeight="1">
+    <row r="107" ht="107" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9480,7 +10284,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr">
@@ -9491,7 +10299,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -9544,7 +10352,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="126" customHeight="1">
+    <row r="108" ht="107" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9568,7 +10376,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
@@ -9579,7 +10391,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -9632,7 +10444,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="126" customHeight="1">
+    <row r="109" ht="107" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9656,7 +10468,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr">
@@ -9667,7 +10483,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -9720,7 +10536,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="126" customHeight="1">
+    <row r="110" ht="107" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9744,7 +10560,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
@@ -9755,7 +10575,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -9808,7 +10628,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="126" customHeight="1">
+    <row r="111" ht="107" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9832,7 +10652,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr"/>
       <c r="I111" s="4" t="inlineStr">
@@ -9843,7 +10667,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -9896,7 +10720,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="126" customHeight="1">
+    <row r="112" ht="107" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9920,7 +10744,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr">
@@ -9931,7 +10759,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -9984,7 +10812,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="126" customHeight="1">
+    <row r="113" ht="107" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10008,7 +10836,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr"/>
       <c r="I113" s="4" t="inlineStr">
@@ -10019,7 +10851,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10072,7 +10904,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="126" customHeight="1">
+    <row r="114" ht="107" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10096,7 +10928,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
@@ -10107,7 +10943,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10160,7 +10996,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="126" customHeight="1">
+    <row r="115" ht="107" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10184,7 +11020,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="inlineStr"/>
       <c r="H115" s="4" t="inlineStr"/>
       <c r="I115" s="4" t="inlineStr">
@@ -10195,7 +11035,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10248,7 +11088,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="126" customHeight="1">
+    <row r="116" ht="107" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10272,7 +11112,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
@@ -10283,7 +11127,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10336,7 +11180,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="126" customHeight="1">
+    <row r="117" ht="107" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10360,7 +11204,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr"/>
       <c r="I117" s="4" t="inlineStr">
@@ -10371,7 +11219,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -10424,7 +11272,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="126" customHeight="1">
+    <row r="118" ht="107" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10448,7 +11296,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr">
@@ -10459,7 +11311,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -10512,7 +11364,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="126" customHeight="1">
+    <row r="119" ht="107" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10536,7 +11388,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr"/>
       <c r="I119" s="4" t="inlineStr">
@@ -10547,7 +11403,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -10600,7 +11456,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="126" customHeight="1">
+    <row r="120" ht="107" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10624,7 +11480,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr">
@@ -10635,7 +11495,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -10688,7 +11548,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="126" customHeight="1">
+    <row r="121" ht="107" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10712,7 +11572,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr"/>
       <c r="I121" s="4" t="inlineStr">
@@ -10723,7 +11587,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -10776,7 +11640,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="126" customHeight="1">
+    <row r="122" ht="107" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10800,7 +11664,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr">
@@ -10811,7 +11679,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -10864,7 +11732,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="126" customHeight="1">
+    <row r="123" ht="107" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10888,7 +11756,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr"/>
       <c r="I123" s="4" t="inlineStr">
@@ -10899,7 +11771,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -10952,7 +11824,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="126" customHeight="1">
+    <row r="124" ht="107" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10976,7 +11848,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr">
@@ -10987,7 +11863,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11040,7 +11916,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="126" customHeight="1">
+    <row r="125" ht="107" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11064,7 +11940,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr"/>
       <c r="I125" s="4" t="inlineStr">
@@ -11075,7 +11955,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11128,7 +12008,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="126" customHeight="1">
+    <row r="126" ht="107" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11152,7 +12032,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr">
@@ -11163,7 +12047,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11216,7 +12100,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="126" customHeight="1">
+    <row r="127" ht="107" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11240,7 +12124,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr"/>
       <c r="I127" s="4" t="inlineStr">
@@ -11251,7 +12139,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11304,7 +12192,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="126" customHeight="1">
+    <row r="128" ht="107" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11328,7 +12216,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr">
@@ -11339,7 +12231,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -11392,7 +12284,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="126" customHeight="1">
+    <row r="129" ht="107" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11416,7 +12308,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr"/>
       <c r="I129" s="4" t="inlineStr">
@@ -11427,7 +12323,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -11480,7 +12376,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="126" customHeight="1">
+    <row r="130" ht="107" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11504,7 +12400,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr">
@@ -11515,7 +12415,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -11568,7 +12468,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="126" customHeight="1">
+    <row r="131" ht="107" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11592,7 +12492,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr"/>
       <c r="I131" s="4" t="inlineStr">
@@ -11603,7 +12507,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -11656,7 +12560,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="126" customHeight="1">
+    <row r="132" ht="107" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11680,7 +12584,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr">
@@ -11691,7 +12599,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -11744,7 +12652,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="126" customHeight="1">
+    <row r="133" ht="107" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11768,7 +12676,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr"/>
       <c r="I133" s="4" t="inlineStr">
@@ -11779,7 +12691,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -11832,7 +12744,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="126" customHeight="1">
+    <row r="134" ht="107" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11856,7 +12768,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr">
@@ -11867,7 +12783,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -11920,7 +12836,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="126" customHeight="1">
+    <row r="135" ht="107" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11944,7 +12860,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr"/>
       <c r="I135" s="4" t="inlineStr">
@@ -11955,7 +12875,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12008,7 +12928,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="126" customHeight="1">
+    <row r="136" ht="107" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12032,7 +12952,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr">
@@ -12043,7 +12967,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -12096,7 +13020,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="126" customHeight="1">
+    <row r="137" ht="107" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12120,7 +13044,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr"/>
       <c r="I137" s="4" t="inlineStr">
@@ -12131,7 +13059,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -12184,7 +13112,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="126" customHeight="1">
+    <row r="138" ht="107" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12208,7 +13136,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr">
@@ -12219,7 +13151,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -12272,7 +13204,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="126" customHeight="1">
+    <row r="139" ht="107" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12296,7 +13228,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr"/>
       <c r="I139" s="4" t="inlineStr">
@@ -12307,7 +13243,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -12360,7 +13296,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="126" customHeight="1">
+    <row r="140" ht="107" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12384,7 +13320,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr">
@@ -12395,7 +13335,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -12448,7 +13388,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="126" customHeight="1">
+    <row r="141" ht="107" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12472,7 +13412,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr"/>
       <c r="I141" s="4" t="inlineStr">
@@ -12483,7 +13427,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -12536,7 +13480,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="126" customHeight="1">
+    <row r="142" ht="107" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12560,7 +13504,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr">
@@ -12571,7 +13519,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -12624,7 +13572,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="126" customHeight="1">
+    <row r="143" ht="107" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12648,7 +13596,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr"/>
       <c r="I143" s="4" t="inlineStr">
@@ -12659,7 +13611,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -12712,7 +13664,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="126" customHeight="1">
+    <row r="144" ht="107" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12736,7 +13688,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
@@ -12747,7 +13703,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -12800,7 +13756,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="126" customHeight="1">
+    <row r="145" ht="107" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12824,7 +13780,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr"/>
       <c r="I145" s="4" t="inlineStr">
@@ -12835,7 +13795,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -12888,7 +13848,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="126" customHeight="1">
+    <row r="146" ht="107" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12912,7 +13872,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
@@ -12923,7 +13887,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -12976,7 +13940,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="126" customHeight="1">
+    <row r="147" ht="107" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13000,7 +13964,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr"/>
       <c r="I147" s="4" t="inlineStr">
@@ -13011,7 +13979,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -13064,7 +14032,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="126" customHeight="1">
+    <row r="148" ht="107" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13088,7 +14056,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr">
@@ -13099,7 +14071,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -13152,7 +14124,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="126" customHeight="1">
+    <row r="149" ht="107" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13176,7 +14148,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr"/>
       <c r="I149" s="4" t="inlineStr">
@@ -13187,7 +14163,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -13240,7 +14216,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="126" customHeight="1">
+    <row r="150" ht="107" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13264,7 +14240,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr">
@@ -13275,7 +14255,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -13328,7 +14308,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="126" customHeight="1">
+    <row r="151" ht="107" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13352,7 +14332,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr"/>
       <c r="I151" s="4" t="inlineStr">
@@ -13363,7 +14347,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -13416,7 +14400,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="126" customHeight="1">
+    <row r="152" ht="107" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13440,7 +14424,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr">
@@ -13451,7 +14439,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -13504,7 +14492,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="126" customHeight="1">
+    <row r="153" ht="107" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13528,7 +14516,11 @@
           <t>Φ60×4</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr"/>
       <c r="I153" s="4" t="inlineStr">
@@ -13539,7 +14531,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">

--- a/data-cleaning/verified/导入_2022年1号机A修.xlsx
+++ b/data-cleaning/verified/导入_2022年1号机A修.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="107" customHeight="1">
+    <row r="2" ht="126" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -611,7 +611,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="107" customHeight="1">
+    <row r="3" ht="126" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="107" customHeight="1">
+    <row r="4" ht="126" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="107" customHeight="1">
+    <row r="5" ht="126" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -887,7 +887,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="107" customHeight="1">
+    <row r="6" ht="126" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -979,7 +979,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="107" customHeight="1">
+    <row r="7" ht="126" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="107" customHeight="1">
+    <row r="8" ht="126" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="107" customHeight="1">
+    <row r="9" ht="126" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="107" customHeight="1">
+    <row r="10" ht="126" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="107" customHeight="1">
+    <row r="11" ht="126" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="107" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="107" customHeight="1">
+    <row r="13" ht="126" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1651,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="107" customHeight="1">
+    <row r="14" ht="126" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="107" customHeight="1">
+    <row r="15" ht="126" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="107" customHeight="1">
+    <row r="16" ht="126" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="107" customHeight="1">
+    <row r="17" ht="126" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2019,7 +2019,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="107" customHeight="1">
+    <row r="18" ht="126" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="107" customHeight="1">
+    <row r="19" ht="126" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="107" customHeight="1">
+    <row r="20" ht="126" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="107" customHeight="1">
+    <row r="21" ht="126" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="107" customHeight="1">
+    <row r="22" ht="126" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="107" customHeight="1">
+    <row r="23" ht="126" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="107" customHeight="1">
+    <row r="24" ht="126" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="107" customHeight="1">
+    <row r="25" ht="126" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2755,7 +2755,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="107" customHeight="1">
+    <row r="26" ht="126" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="107" customHeight="1">
+    <row r="27" ht="126" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="107" customHeight="1">
+    <row r="28" ht="126" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3031,7 +3031,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="107" customHeight="1">
+    <row r="29" ht="126" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3123,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="107" customHeight="1">
+    <row r="30" ht="126" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3215,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="107" customHeight="1">
+    <row r="31" ht="126" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3307,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="107" customHeight="1">
+    <row r="32" ht="126" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="107" customHeight="1">
+    <row r="33" ht="126" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
@@ -3544,7 +3544,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="107" customHeight="1">
+    <row r="34" ht="126" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -3583,7 +3583,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="107" customHeight="1">
+    <row r="35" ht="126" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="107" customHeight="1">
+    <row r="36" ht="126" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -3767,7 +3767,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="107" customHeight="1">
+    <row r="37" ht="126" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3859,7 +3859,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="107" customHeight="1">
+    <row r="38" ht="126" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="107" customHeight="1">
+    <row r="39" ht="126" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4043,7 +4043,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="107" customHeight="1">
+    <row r="40" ht="126" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="107" customHeight="1">
+    <row r="41" ht="126" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4227,7 +4227,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="107" customHeight="1">
+    <row r="42" ht="126" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="107" customHeight="1">
+    <row r="43" ht="126" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4411,7 +4411,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T43" s="4" t="inlineStr">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="107" customHeight="1">
+    <row r="44" ht="126" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="107" customHeight="1">
+    <row r="45" ht="126" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="107" customHeight="1">
+    <row r="46" ht="126" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -4740,7 +4740,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="107" customHeight="1">
+    <row r="47" ht="126" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="107" customHeight="1">
+    <row r="48" ht="126" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -4871,7 +4871,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="107" customHeight="1">
+    <row r="49" ht="126" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4963,7 +4963,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="107" customHeight="1">
+    <row r="50" ht="126" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="107" customHeight="1">
+    <row r="51" ht="126" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5147,7 +5147,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T51" s="4" t="inlineStr">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="107" customHeight="1">
+    <row r="52" ht="126" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="107" customHeight="1">
+    <row r="53" ht="126" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5331,7 +5331,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr">
@@ -5384,7 +5384,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="107" customHeight="1">
+    <row r="54" ht="126" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="107" customHeight="1">
+    <row r="55" ht="126" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5515,7 +5515,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
@@ -5568,7 +5568,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="107" customHeight="1">
+    <row r="56" ht="126" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="107" customHeight="1">
+    <row r="57" ht="126" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="107" customHeight="1">
+    <row r="58" ht="126" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -5791,7 +5791,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="107" customHeight="1">
+    <row r="59" ht="126" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -5883,7 +5883,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="107" customHeight="1">
+    <row r="60" ht="126" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="107" customHeight="1">
+    <row r="61" ht="126" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6067,7 +6067,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T61" s="4" t="inlineStr">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="107" customHeight="1">
+    <row r="62" ht="126" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -6159,7 +6159,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="107" customHeight="1">
+    <row r="63" ht="126" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6251,7 +6251,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T63" s="4" t="inlineStr">
@@ -6304,7 +6304,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="107" customHeight="1">
+    <row r="64" ht="126" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="107" customHeight="1">
+    <row r="65" ht="126" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6435,7 +6435,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="107" customHeight="1">
+    <row r="66" ht="126" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="107" customHeight="1">
+    <row r="67" ht="126" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6619,7 +6619,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="107" customHeight="1">
+    <row r="68" ht="126" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="107" customHeight="1">
+    <row r="69" ht="126" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -6803,7 +6803,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="107" customHeight="1">
+    <row r="70" ht="126" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -6895,7 +6895,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="107" customHeight="1">
+    <row r="71" ht="126" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -6987,7 +6987,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr">
@@ -7040,7 +7040,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="107" customHeight="1">
+    <row r="72" ht="126" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="107" customHeight="1">
+    <row r="73" ht="126" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7171,7 +7171,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="107" customHeight="1">
+    <row r="74" ht="126" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -7263,7 +7263,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="107" customHeight="1">
+    <row r="75" ht="126" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7355,7 +7355,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr">
@@ -7408,7 +7408,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="107" customHeight="1">
+    <row r="76" ht="126" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -7447,7 +7447,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="107" customHeight="1">
+    <row r="77" ht="126" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7539,7 +7539,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T77" s="4" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="107" customHeight="1">
+    <row r="78" ht="126" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="107" customHeight="1">
+    <row r="79" ht="126" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7723,7 +7723,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T79" s="4" t="inlineStr">
@@ -7776,7 +7776,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="107" customHeight="1">
+    <row r="80" ht="126" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="107" customHeight="1">
+    <row r="81" ht="126" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -7907,7 +7907,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T81" s="4" t="inlineStr">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="107" customHeight="1">
+    <row r="82" ht="126" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -7999,7 +7999,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="107" customHeight="1">
+    <row r="83" ht="126" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -8091,7 +8091,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T83" s="4" t="inlineStr">
@@ -8144,7 +8144,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="107" customHeight="1">
+    <row r="84" ht="126" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -8183,7 +8183,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="107" customHeight="1">
+    <row r="85" ht="126" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8275,7 +8275,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T85" s="4" t="inlineStr">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="107" customHeight="1">
+    <row r="86" ht="126" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -8367,7 +8367,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP347H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→SA-213TP347H</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="107" customHeight="1">
+    <row r="87" ht="126" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8459,7 +8459,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr">
@@ -8512,7 +8512,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="107" customHeight="1">
+    <row r="88" ht="126" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="107" customHeight="1">
+    <row r="89" ht="126" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8643,7 +8643,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T89" s="4" t="inlineStr">
@@ -8696,7 +8696,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="107" customHeight="1">
+    <row r="90" ht="126" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="107" customHeight="1">
+    <row r="91" ht="126" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8827,7 +8827,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T91" s="4" t="inlineStr">
@@ -8880,7 +8880,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="107" customHeight="1">
+    <row r="92" ht="126" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="107" customHeight="1">
+    <row r="93" ht="126" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -9011,7 +9011,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F008=第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T93" s="4" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="107" customHeight="1">
+    <row r="94" ht="126" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F009=第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="107" customHeight="1">
+    <row r="95" ht="126" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -9195,7 +9195,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F010=第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T95" s="4" t="inlineStr">
@@ -9248,7 +9248,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="107" customHeight="1">
+    <row r="96" ht="126" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -9287,7 +9287,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F011=第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="107" customHeight="1">
+    <row r="97" ht="126" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9379,7 +9379,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T97" s="4" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9563,7 +9563,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T99" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9747,7 +9747,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T101" s="4" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
@@ -9839,7 +9839,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -9931,7 +9931,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T103" s="4" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -10115,7 +10115,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T105" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -10299,7 +10299,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T107" s="4" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -10483,7 +10483,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T109" s="4" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
@@ -10575,7 +10575,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T111" s="4" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T112" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -10851,7 +10851,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T113" s="4" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -10943,7 +10943,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T114" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -11035,7 +11035,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T115" s="4" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
@@ -11127,7 +11127,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -11219,7 +11219,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T117" s="4" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -11403,7 +11403,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -11587,7 +11587,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T121" s="4" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T122" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T123" s="4" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
@@ -11863,7 +11863,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T124" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T125" s="4" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T126" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -12139,7 +12139,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T127" s="4" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -12231,7 +12231,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -12323,7 +12323,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -12357,7 +12357,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T129" s="4" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -12507,7 +12507,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T131" s="4" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
@@ -12599,7 +12599,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -12691,7 +12691,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T133" s="4" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -12783,7 +12783,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T134" s="2" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -12875,7 +12875,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T135" s="4" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -12967,7 +12967,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -13059,7 +13059,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T137" s="4" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
@@ -13151,7 +13151,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T138" s="2" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
@@ -13243,7 +13243,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T139" s="4" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -13335,7 +13335,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="S140" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T140" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -13427,7 +13427,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T141" s="4" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -13519,7 +13519,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="S142" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T142" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -13611,7 +13611,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T143" s="4" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
@@ -13703,7 +13703,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T144" s="2" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -13795,7 +13795,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T145" s="4" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -13887,7 +13887,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T146" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -13979,7 +13979,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T147" s="4" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -14071,7 +14071,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T148" s="2" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -14163,7 +14163,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T149" s="4" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -14255,7 +14255,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="S150" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T150" s="2" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
@@ -14347,7 +14347,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T151" s="4" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="S152" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T152" s="2" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
@@ -14531,7 +14531,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12CrMoVG</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T153" s="4" t="inlineStr">

--- a/data-cleaning/verified/导入_2022年1号机A修.xlsx
+++ b/data-cleaning/verified/导入_2022年1号机A修.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1191,7 +1191,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -3215,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -3859,7 +3859,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -4319,7 +4319,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -4503,7 +4503,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -5515,7 +5515,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -6067,7 +6067,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -6711,7 +6711,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -7723,7 +7723,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
@@ -7815,7 +7815,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
@@ -8827,7 +8827,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -9379,7 +9379,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -9563,7 +9563,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -9655,7 +9655,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -9747,7 +9747,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
@@ -10207,7 +10207,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -10299,7 +10299,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -10391,7 +10391,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -10851,7 +10851,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
@@ -10943,7 +10943,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -11035,7 +11035,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
@@ -11495,7 +11495,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -11587,7 +11587,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
@@ -11679,7 +11679,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
@@ -12139,7 +12139,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
@@ -12231,7 +12231,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
@@ -12783,7 +12783,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -12875,7 +12875,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
@@ -12967,7 +12967,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
@@ -13427,7 +13427,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -13611,7 +13611,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
@@ -14255,7 +14255,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">

--- a/data-cleaning/verified/导入_2022年1号机A修.xlsx
+++ b/data-cleaning/verified/导入_2022年1号机A修.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="126" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -600,7 +600,7 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="126" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -692,7 +692,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="126" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -784,7 +784,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="126" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -876,7 +876,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="126" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -968,7 +968,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="126" customHeight="1">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1060,7 +1060,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="126" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1152,7 +1152,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="126" customHeight="1">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1244,7 +1244,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="126" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1336,7 +1336,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="126" customHeight="1">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1428,7 +1428,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1520,7 +1520,7 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="126" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1612,7 +1612,7 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="126" customHeight="1">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1704,7 +1704,7 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="126" customHeight="1">
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1796,7 +1796,7 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="126" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1888,7 +1888,7 @@
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="126" customHeight="1">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1980,7 +1980,7 @@
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="126" customHeight="1">
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2072,7 +2072,7 @@
       <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="126" customHeight="1">
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2164,7 +2164,7 @@
       <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="126" customHeight="1">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2256,7 +2256,7 @@
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="126" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2348,7 +2348,7 @@
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="126" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2440,7 +2440,7 @@
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="126" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2532,7 +2532,7 @@
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="126" customHeight="1">
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2624,7 +2624,7 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="126" customHeight="1">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2716,7 +2716,7 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="126" customHeight="1">
+    <row r="26" ht="32" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2808,7 +2808,7 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="126" customHeight="1">
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2900,7 +2900,7 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="126" customHeight="1">
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2992,7 +2992,7 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="126" customHeight="1">
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3084,7 +3084,7 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="126" customHeight="1">
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3176,7 +3176,7 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="126" customHeight="1">
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3268,7 +3268,7 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="126" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3360,7 +3360,7 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="126" customHeight="1">
+    <row r="33" ht="32" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3452,7 +3452,7 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="126" customHeight="1">
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3544,7 +3544,7 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="126" customHeight="1">
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3636,7 +3636,7 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr">
@@ -3689,7 +3689,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="126" customHeight="1">
+    <row r="36" ht="32" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3728,7 +3728,7 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="126" customHeight="1">
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3820,7 +3820,7 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="126" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3912,7 +3912,7 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="126" customHeight="1">
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4004,7 +4004,7 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="126" customHeight="1">
+    <row r="40" ht="32" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4096,7 +4096,7 @@
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L40" s="1" t="inlineStr">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="126" customHeight="1">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4188,7 +4188,7 @@
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L41" s="1" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="126" customHeight="1">
+    <row r="42" ht="32" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4280,7 +4280,7 @@
       <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="126" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4372,7 +4372,7 @@
       <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L43" s="1" t="inlineStr">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="126" customHeight="1">
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4464,7 +4464,7 @@
       <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="126" customHeight="1">
+    <row r="45" ht="32" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4556,7 +4556,7 @@
       <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="126" customHeight="1">
+    <row r="46" ht="32" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4648,7 +4648,7 @@
       <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="126" customHeight="1">
+    <row r="47" ht="32" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4740,7 +4740,7 @@
       <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="126" customHeight="1">
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4832,7 +4832,7 @@
       <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="126" customHeight="1">
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4924,7 +4924,7 @@
       <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L49" s="1" t="inlineStr">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="126" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5016,7 +5016,7 @@
       <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="126" customHeight="1">
+    <row r="51" ht="32" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5108,7 +5108,7 @@
       <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="126" customHeight="1">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5200,7 +5200,7 @@
       <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="126" customHeight="1">
+    <row r="53" ht="32" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5292,7 +5292,7 @@
       <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="126" customHeight="1">
+    <row r="54" ht="32" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5384,7 +5384,7 @@
       <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="126" customHeight="1">
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5476,7 +5476,7 @@
       <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -5529,7 +5529,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="126" customHeight="1">
+    <row r="56" ht="32" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5568,7 +5568,7 @@
       <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="126" customHeight="1">
+    <row r="57" ht="32" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5660,7 +5660,7 @@
       <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="126" customHeight="1">
+    <row r="58" ht="32" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5752,7 +5752,7 @@
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="126" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5844,7 +5844,7 @@
       <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="126" customHeight="1">
+    <row r="60" ht="32" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5936,7 +5936,7 @@
       <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L60" s="1" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="126" customHeight="1">
+    <row r="61" ht="32" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6028,7 +6028,7 @@
       <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L61" s="1" t="inlineStr">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="126" customHeight="1">
+    <row r="62" ht="32" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6120,7 +6120,7 @@
       <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="126" customHeight="1">
+    <row r="63" ht="32" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6212,7 +6212,7 @@
       <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L63" s="1" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="126" customHeight="1">
+    <row r="64" ht="32" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6304,7 +6304,7 @@
       <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
@@ -6357,7 +6357,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="126" customHeight="1">
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6396,7 +6396,7 @@
       <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="126" customHeight="1">
+    <row r="66" ht="32" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6488,7 +6488,7 @@
       <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L66" s="1" t="inlineStr">
@@ -6541,7 +6541,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="126" customHeight="1">
+    <row r="67" ht="32" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6580,7 +6580,7 @@
       <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
@@ -6633,7 +6633,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="126" customHeight="1">
+    <row r="68" ht="32" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6672,7 +6672,7 @@
       <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L68" s="1" t="inlineStr">
@@ -6725,7 +6725,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="126" customHeight="1">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6764,7 +6764,7 @@
       <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L69" s="1" t="inlineStr">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="126" customHeight="1">
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6856,7 +6856,7 @@
       <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L70" s="1" t="inlineStr">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="126" customHeight="1">
+    <row r="71" ht="32" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6948,7 +6948,7 @@
       <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L71" s="1" t="inlineStr">
@@ -7001,7 +7001,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="126" customHeight="1">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7040,7 +7040,7 @@
       <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L72" s="1" t="inlineStr">
@@ -7093,7 +7093,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="126" customHeight="1">
+    <row r="73" ht="32" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7132,7 +7132,7 @@
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L73" s="1" t="inlineStr">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="126" customHeight="1">
+    <row r="74" ht="32" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7224,7 +7224,7 @@
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L74" s="1" t="inlineStr">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="126" customHeight="1">
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7316,7 +7316,7 @@
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L75" s="1" t="inlineStr">
@@ -7369,7 +7369,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="126" customHeight="1">
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7408,7 +7408,7 @@
       <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L76" s="1" t="inlineStr">
@@ -7461,7 +7461,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="126" customHeight="1">
+    <row r="77" ht="32" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7500,7 +7500,7 @@
       <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L77" s="1" t="inlineStr">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="126" customHeight="1">
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7592,7 +7592,7 @@
       <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L78" s="1" t="inlineStr">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="126" customHeight="1">
+    <row r="79" ht="32" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7684,7 +7684,7 @@
       <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L79" s="1" t="inlineStr">
@@ -7737,7 +7737,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="126" customHeight="1">
+    <row r="80" ht="32" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7776,7 +7776,7 @@
       <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L80" s="1" t="inlineStr">
@@ -7829,7 +7829,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="126" customHeight="1">
+    <row r="81" ht="32" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7868,7 +7868,7 @@
       <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L81" s="1" t="inlineStr">
@@ -7921,7 +7921,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="126" customHeight="1">
+    <row r="82" ht="32" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7960,7 +7960,7 @@
       <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L82" s="1" t="inlineStr">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="126" customHeight="1">
+    <row r="83" ht="32" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8052,7 +8052,7 @@
       <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L83" s="1" t="inlineStr">
@@ -8105,7 +8105,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="126" customHeight="1">
+    <row r="84" ht="32" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8144,7 +8144,7 @@
       <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L84" s="1" t="inlineStr">
@@ -8197,7 +8197,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="126" customHeight="1">
+    <row r="85" ht="32" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8236,7 +8236,7 @@
       <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L85" s="1" t="inlineStr">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="126" customHeight="1">
+    <row r="86" ht="32" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8328,7 +8328,7 @@
       <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L86" s="1" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="126" customHeight="1">
+    <row r="87" ht="32" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8420,7 +8420,7 @@
       <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L87" s="1" t="inlineStr">
@@ -8473,7 +8473,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="126" customHeight="1">
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8512,7 +8512,7 @@
       <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L88" s="1" t="inlineStr">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="126" customHeight="1">
+    <row r="89" ht="32" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8604,7 +8604,7 @@
       <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L89" s="1" t="inlineStr">
@@ -8657,7 +8657,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="126" customHeight="1">
+    <row r="90" ht="32" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8696,7 +8696,7 @@
       <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L90" s="1" t="inlineStr">
@@ -8749,7 +8749,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="126" customHeight="1">
+    <row r="91" ht="32" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8788,7 +8788,7 @@
       <c r="J91" s="1" t="inlineStr"/>
       <c r="K91" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L91" s="1" t="inlineStr">
@@ -8841,7 +8841,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="126" customHeight="1">
+    <row r="92" ht="32" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8880,7 +8880,7 @@
       <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L92" s="1" t="inlineStr">
@@ -8933,7 +8933,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="126" customHeight="1">
+    <row r="93" ht="32" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8972,7 +8972,7 @@
       <c r="J93" s="1" t="inlineStr"/>
       <c r="K93" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L93" s="1" t="inlineStr">
@@ -9025,7 +9025,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="126" customHeight="1">
+    <row r="94" ht="32" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9064,7 +9064,7 @@
       <c r="J94" s="1" t="inlineStr"/>
       <c r="K94" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L94" s="1" t="inlineStr">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="126" customHeight="1">
+    <row r="95" ht="32" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9156,7 +9156,7 @@
       <c r="J95" s="1" t="inlineStr"/>
       <c r="K95" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L95" s="1" t="inlineStr">
@@ -9209,7 +9209,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="126" customHeight="1">
+    <row r="96" ht="32" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9248,7 +9248,7 @@
       <c r="J96" s="1" t="inlineStr"/>
       <c r="K96" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L96" s="1" t="inlineStr">
@@ -9301,7 +9301,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="126" customHeight="1">
+    <row r="97" ht="32" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9340,7 +9340,7 @@
       <c r="J97" s="1" t="inlineStr"/>
       <c r="K97" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L97" s="1" t="inlineStr">
@@ -9393,7 +9393,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="107" customHeight="1">
+    <row r="98" ht="32" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9432,7 +9432,7 @@
       <c r="J98" s="1" t="inlineStr"/>
       <c r="K98" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L98" s="1" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="107" customHeight="1">
+    <row r="99" ht="32" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9524,7 +9524,7 @@
       <c r="J99" s="1" t="inlineStr"/>
       <c r="K99" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L99" s="1" t="inlineStr">
@@ -9577,7 +9577,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="107" customHeight="1">
+    <row r="100" ht="32" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9616,7 +9616,7 @@
       <c r="J100" s="1" t="inlineStr"/>
       <c r="K100" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L100" s="1" t="inlineStr">
@@ -9669,7 +9669,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="107" customHeight="1">
+    <row r="101" ht="32" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9708,7 +9708,7 @@
       <c r="J101" s="1" t="inlineStr"/>
       <c r="K101" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L101" s="1" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="107" customHeight="1">
+    <row r="102" ht="32" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9800,7 +9800,7 @@
       <c r="J102" s="1" t="inlineStr"/>
       <c r="K102" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L102" s="1" t="inlineStr">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="107" customHeight="1">
+    <row r="103" ht="32" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9892,7 +9892,7 @@
       <c r="J103" s="1" t="inlineStr"/>
       <c r="K103" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L103" s="1" t="inlineStr">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="107" customHeight="1">
+    <row r="104" ht="32" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9984,7 +9984,7 @@
       <c r="J104" s="1" t="inlineStr"/>
       <c r="K104" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L104" s="1" t="inlineStr">
@@ -10037,7 +10037,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="107" customHeight="1">
+    <row r="105" ht="32" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10076,7 +10076,7 @@
       <c r="J105" s="1" t="inlineStr"/>
       <c r="K105" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L105" s="1" t="inlineStr">
@@ -10129,7 +10129,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="107" customHeight="1">
+    <row r="106" ht="32" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10168,7 +10168,7 @@
       <c r="J106" s="1" t="inlineStr"/>
       <c r="K106" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L106" s="1" t="inlineStr">
@@ -10221,7 +10221,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="107" customHeight="1">
+    <row r="107" ht="32" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10260,7 +10260,7 @@
       <c r="J107" s="1" t="inlineStr"/>
       <c r="K107" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L107" s="1" t="inlineStr">
@@ -10313,7 +10313,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="107" customHeight="1">
+    <row r="108" ht="32" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10352,7 +10352,7 @@
       <c r="J108" s="1" t="inlineStr"/>
       <c r="K108" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L108" s="1" t="inlineStr">
@@ -10405,7 +10405,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="107" customHeight="1">
+    <row r="109" ht="32" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10444,7 +10444,7 @@
       <c r="J109" s="1" t="inlineStr"/>
       <c r="K109" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L109" s="1" t="inlineStr">
@@ -10497,7 +10497,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="107" customHeight="1">
+    <row r="110" ht="32" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10536,7 +10536,7 @@
       <c r="J110" s="1" t="inlineStr"/>
       <c r="K110" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L110" s="1" t="inlineStr">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="107" customHeight="1">
+    <row r="111" ht="32" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10628,7 +10628,7 @@
       <c r="J111" s="1" t="inlineStr"/>
       <c r="K111" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L111" s="1" t="inlineStr">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="107" customHeight="1">
+    <row r="112" ht="32" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10720,7 +10720,7 @@
       <c r="J112" s="1" t="inlineStr"/>
       <c r="K112" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L112" s="1" t="inlineStr">
@@ -10773,7 +10773,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="107" customHeight="1">
+    <row r="113" ht="32" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10812,7 +10812,7 @@
       <c r="J113" s="1" t="inlineStr"/>
       <c r="K113" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L113" s="1" t="inlineStr">
@@ -10865,7 +10865,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="107" customHeight="1">
+    <row r="114" ht="32" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10904,7 +10904,7 @@
       <c r="J114" s="1" t="inlineStr"/>
       <c r="K114" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L114" s="1" t="inlineStr">
@@ -10957,7 +10957,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="107" customHeight="1">
+    <row r="115" ht="32" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10996,7 +10996,7 @@
       <c r="J115" s="1" t="inlineStr"/>
       <c r="K115" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L115" s="1" t="inlineStr">
@@ -11049,7 +11049,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="107" customHeight="1">
+    <row r="116" ht="32" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11088,7 +11088,7 @@
       <c r="J116" s="1" t="inlineStr"/>
       <c r="K116" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L116" s="1" t="inlineStr">
@@ -11141,7 +11141,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="107" customHeight="1">
+    <row r="117" ht="32" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11180,7 +11180,7 @@
       <c r="J117" s="1" t="inlineStr"/>
       <c r="K117" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L117" s="1" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="107" customHeight="1">
+    <row r="118" ht="32" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11272,7 +11272,7 @@
       <c r="J118" s="1" t="inlineStr"/>
       <c r="K118" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L118" s="1" t="inlineStr">
@@ -11325,7 +11325,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="107" customHeight="1">
+    <row r="119" ht="32" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11364,7 +11364,7 @@
       <c r="J119" s="1" t="inlineStr"/>
       <c r="K119" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L119" s="1" t="inlineStr">
@@ -11417,7 +11417,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="107" customHeight="1">
+    <row r="120" ht="32" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11456,7 +11456,7 @@
       <c r="J120" s="1" t="inlineStr"/>
       <c r="K120" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L120" s="1" t="inlineStr">
@@ -11509,7 +11509,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="107" customHeight="1">
+    <row r="121" ht="32" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11548,7 +11548,7 @@
       <c r="J121" s="1" t="inlineStr"/>
       <c r="K121" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L121" s="1" t="inlineStr">
@@ -11601,7 +11601,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="107" customHeight="1">
+    <row r="122" ht="32" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11640,7 +11640,7 @@
       <c r="J122" s="1" t="inlineStr"/>
       <c r="K122" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L122" s="1" t="inlineStr">
@@ -11693,7 +11693,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="107" customHeight="1">
+    <row r="123" ht="32" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11732,7 +11732,7 @@
       <c r="J123" s="1" t="inlineStr"/>
       <c r="K123" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L123" s="1" t="inlineStr">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="107" customHeight="1">
+    <row r="124" ht="32" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11824,7 +11824,7 @@
       <c r="J124" s="1" t="inlineStr"/>
       <c r="K124" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L124" s="1" t="inlineStr">
@@ -11877,7 +11877,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="107" customHeight="1">
+    <row r="125" ht="32" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11916,7 +11916,7 @@
       <c r="J125" s="1" t="inlineStr"/>
       <c r="K125" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L125" s="1" t="inlineStr">
@@ -11969,7 +11969,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="107" customHeight="1">
+    <row r="126" ht="32" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12008,7 +12008,7 @@
       <c r="J126" s="1" t="inlineStr"/>
       <c r="K126" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L126" s="1" t="inlineStr">
@@ -12061,7 +12061,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="107" customHeight="1">
+    <row r="127" ht="32" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12100,7 +12100,7 @@
       <c r="J127" s="1" t="inlineStr"/>
       <c r="K127" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L127" s="1" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="107" customHeight="1">
+    <row r="128" ht="32" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12192,7 +12192,7 @@
       <c r="J128" s="1" t="inlineStr"/>
       <c r="K128" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L128" s="1" t="inlineStr">
@@ -12245,7 +12245,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="107" customHeight="1">
+    <row r="129" ht="32" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12284,7 +12284,7 @@
       <c r="J129" s="1" t="inlineStr"/>
       <c r="K129" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L129" s="1" t="inlineStr">
@@ -12337,7 +12337,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="107" customHeight="1">
+    <row r="130" ht="32" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12376,7 +12376,7 @@
       <c r="J130" s="1" t="inlineStr"/>
       <c r="K130" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L130" s="1" t="inlineStr">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="107" customHeight="1">
+    <row r="131" ht="32" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12468,7 +12468,7 @@
       <c r="J131" s="1" t="inlineStr"/>
       <c r="K131" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L131" s="1" t="inlineStr">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="107" customHeight="1">
+    <row r="132" ht="32" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12560,7 +12560,7 @@
       <c r="J132" s="1" t="inlineStr"/>
       <c r="K132" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L132" s="1" t="inlineStr">
@@ -12613,7 +12613,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="107" customHeight="1">
+    <row r="133" ht="32" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12652,7 +12652,7 @@
       <c r="J133" s="1" t="inlineStr"/>
       <c r="K133" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L133" s="1" t="inlineStr">
@@ -12705,7 +12705,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="107" customHeight="1">
+    <row r="134" ht="32" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12744,7 +12744,7 @@
       <c r="J134" s="1" t="inlineStr"/>
       <c r="K134" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L134" s="1" t="inlineStr">
@@ -12797,7 +12797,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="107" customHeight="1">
+    <row r="135" ht="32" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12836,7 +12836,7 @@
       <c r="J135" s="1" t="inlineStr"/>
       <c r="K135" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L135" s="1" t="inlineStr">
@@ -12889,7 +12889,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="107" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12928,7 +12928,7 @@
       <c r="J136" s="1" t="inlineStr"/>
       <c r="K136" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L136" s="1" t="inlineStr">
@@ -12981,7 +12981,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="107" customHeight="1">
+    <row r="137" ht="32" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13020,7 +13020,7 @@
       <c r="J137" s="1" t="inlineStr"/>
       <c r="K137" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L137" s="1" t="inlineStr">
@@ -13073,7 +13073,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="107" customHeight="1">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13112,7 +13112,7 @@
       <c r="J138" s="1" t="inlineStr"/>
       <c r="K138" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L138" s="1" t="inlineStr">
@@ -13165,7 +13165,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="107" customHeight="1">
+    <row r="139" ht="32" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13204,7 +13204,7 @@
       <c r="J139" s="1" t="inlineStr"/>
       <c r="K139" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L139" s="1" t="inlineStr">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="107" customHeight="1">
+    <row r="140" ht="32" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13296,7 +13296,7 @@
       <c r="J140" s="1" t="inlineStr"/>
       <c r="K140" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L140" s="1" t="inlineStr">
@@ -13349,7 +13349,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="107" customHeight="1">
+    <row r="141" ht="32" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13388,7 +13388,7 @@
       <c r="J141" s="1" t="inlineStr"/>
       <c r="K141" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L141" s="1" t="inlineStr">
@@ -13441,7 +13441,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="107" customHeight="1">
+    <row r="142" ht="32" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13480,7 +13480,7 @@
       <c r="J142" s="1" t="inlineStr"/>
       <c r="K142" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L142" s="1" t="inlineStr">
@@ -13533,7 +13533,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="107" customHeight="1">
+    <row r="143" ht="32" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13572,7 +13572,7 @@
       <c r="J143" s="1" t="inlineStr"/>
       <c r="K143" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L143" s="1" t="inlineStr">
@@ -13625,7 +13625,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="107" customHeight="1">
+    <row r="144" ht="32" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13664,7 +13664,7 @@
       <c r="J144" s="1" t="inlineStr"/>
       <c r="K144" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L144" s="1" t="inlineStr">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="107" customHeight="1">
+    <row r="145" ht="32" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13756,7 +13756,7 @@
       <c r="J145" s="1" t="inlineStr"/>
       <c r="K145" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L145" s="1" t="inlineStr">
@@ -13809,7 +13809,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="107" customHeight="1">
+    <row r="146" ht="32" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13848,7 +13848,7 @@
       <c r="J146" s="1" t="inlineStr"/>
       <c r="K146" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L146" s="1" t="inlineStr">
@@ -13901,7 +13901,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="107" customHeight="1">
+    <row r="147" ht="32" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13940,7 +13940,7 @@
       <c r="J147" s="1" t="inlineStr"/>
       <c r="K147" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L147" s="1" t="inlineStr">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="107" customHeight="1">
+    <row r="148" ht="32" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14032,7 +14032,7 @@
       <c r="J148" s="1" t="inlineStr"/>
       <c r="K148" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L148" s="1" t="inlineStr">
@@ -14085,7 +14085,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="107" customHeight="1">
+    <row r="149" ht="32" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14124,7 +14124,7 @@
       <c r="J149" s="1" t="inlineStr"/>
       <c r="K149" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L149" s="1" t="inlineStr">
@@ -14177,7 +14177,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="107" customHeight="1">
+    <row r="150" ht="32" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14216,7 +14216,7 @@
       <c r="J150" s="1" t="inlineStr"/>
       <c r="K150" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L150" s="1" t="inlineStr">
@@ -14269,7 +14269,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="107" customHeight="1">
+    <row r="151" ht="32" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14308,7 +14308,7 @@
       <c r="J151" s="1" t="inlineStr"/>
       <c r="K151" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L151" s="1" t="inlineStr">
@@ -14361,7 +14361,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="107" customHeight="1">
+    <row r="152" ht="32" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14400,7 +14400,7 @@
       <c r="J152" s="1" t="inlineStr"/>
       <c r="K152" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L152" s="1" t="inlineStr">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="107" customHeight="1">
+    <row r="153" ht="32" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14492,7 +14492,7 @@
       <c r="J153" s="1" t="inlineStr"/>
       <c r="K153" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L153" s="1" t="inlineStr">
